--- a/data/trans_dic/P15E_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,32; 83,9</t>
+          <t>11,23; 82,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,13; 89,28</t>
+          <t>56,33; 89,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,27; 81,75</t>
+          <t>48,17; 80,57</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 84,24</t>
+          <t>16,73; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,07; 96,11</t>
+          <t>68,63; 96,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,86; 90,77</t>
+          <t>54,39; 90,58</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,61; 87,7</t>
+          <t>35,99; 87,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,5; 66,24</t>
+          <t>22,31; 65,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,46; 68,7</t>
+          <t>36,08; 68,02</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,23; 91,32</t>
+          <t>35,85; 91,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,59; 94,17</t>
+          <t>48,59; 94,39</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57,5; 94,75</t>
+          <t>58,0; 95,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58,58; 84,71</t>
+          <t>57,08; 85,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,99; 84,97</t>
+          <t>64,69; 85,73</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,25; 85,94</t>
+          <t>13,47; 85,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,61; 89,55</t>
+          <t>56,58; 89,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54,75; 83,51</t>
+          <t>53,88; 83,32</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,11; 91,88</t>
+          <t>34,55; 91,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,52; 87,67</t>
+          <t>37,13; 86,44</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50,5; 76,16</t>
+          <t>50,07; 77,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63,63; 78,28</t>
+          <t>64,85; 78,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63,36; 75,95</t>
+          <t>63,4; 75,62</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>644; 4389</t>
+          <t>587; 4300</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7704; 12254</t>
+          <t>7731; 12268</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9339; 15496</t>
+          <t>9132; 15273</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>868; 4418</t>
+          <t>877; 5245</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8706; 12664</t>
+          <t>9042; 12684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10474; 16721</t>
+          <t>10020; 16685</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2843; 7000</t>
+          <t>2873; 6948</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2569; 7240</t>
+          <t>2439; 7172</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6895; 12992</t>
+          <t>6823; 12865</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1326; 2080</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2047; 4227</t>
+          <t>1659; 4227</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3528; 6317</t>
+          <t>3260; 6332</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>831; 1495</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>123; 540</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1297; 2035</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3858; 6357</t>
+          <t>3891; 6383</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9099; 13159</t>
+          <t>8866; 13217</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14233; 18898</t>
+          <t>14389; 19069</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>654; 3944</t>
+          <t>618; 3936</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9871; 15614</t>
+          <t>9866; 15624</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12059; 18392</t>
+          <t>11866; 18350</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2225; 6177</t>
+          <t>2322; 6164</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2814; 6575</t>
+          <t>2784; 6483</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17224; 25976</t>
+          <t>17080; 26406</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>52617; 64726</t>
+          <t>53627; 64833</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74001; 88709</t>
+          <t>74045; 88323</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15E_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,23; 82,21</t>
+          <t>24,02; 87,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,33; 89,38</t>
+          <t>53,94; 89,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,17; 80,57</t>
+          <t>52,22; 83,41</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 100,0</t>
+          <t>16,64; 84,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,63; 96,27</t>
+          <t>68,29; 96,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,39; 90,58</t>
+          <t>57,21; 90,95</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,99; 87,05</t>
+          <t>35,81; 86,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,31; 65,61</t>
+          <t>24,01; 65,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,08; 68,02</t>
+          <t>34,44; 67,64</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,85; 91,35</t>
+          <t>36,63; 91,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,59; 94,39</t>
+          <t>61,7; 95,26</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,0; 95,14</t>
+          <t>57,0; 94,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,08; 85,09</t>
+          <t>59,89; 85,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,69; 85,73</t>
+          <t>63,27; 85,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,47; 85,77</t>
+          <t>13,58; 87,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,58; 89,61</t>
+          <t>60,9; 90,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,88; 83,32</t>
+          <t>55,09; 83,97</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,55; 91,69</t>
+          <t>35,98; 92,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,13; 86,44</t>
+          <t>37,93; 87,06</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50,07; 77,42</t>
+          <t>50,16; 75,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64,85; 78,41</t>
+          <t>65,92; 79,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63,4; 75,62</t>
+          <t>64,34; 76,08</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>13339</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>587; 4300</t>
+          <t>1378; 5011</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7731; 12268</t>
+          <t>7492; 12428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9132; 15273</t>
+          <t>10250; 16370</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>15034</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>877; 5245</t>
+          <t>947; 4802</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9042; 12684</t>
+          <t>9480; 13347</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10020; 16685</t>
+          <t>11198; 17802</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9998</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2873; 6948</t>
+          <t>2848; 6891</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2439; 7172</t>
+          <t>2662; 7285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6823; 12865</t>
+          <t>6557; 12879</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>6434</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1659; 4227</t>
+          <t>1778; 4443</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3260; 6332</t>
+          <t>4790; 7395</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17171</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3891; 6383</t>
+          <t>3823; 6362</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8866; 13217</t>
+          <t>9507; 13501</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14389; 19069</t>
+          <t>14287; 19360</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>19410</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>618; 3936</t>
+          <t>847; 5447</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9866; 15624</t>
+          <t>12955; 19283</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11866; 18350</t>
+          <t>15157; 23101</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>667</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5847</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>0; 1326</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2322; 6164</t>
+          <t>2743; 7015</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2784; 6483</t>
+          <t>3394; 7791</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89295</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17080; 26406</t>
+          <t>19114; 28837</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53627; 64833</t>
+          <t>58671; 70528</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74045; 88323</t>
+          <t>81785; 96701</t>
         </is>
       </c>
     </row>
